--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akrao\OneDrive\Documents\UiPath\Assignment-13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42CFE50-F9BC-4A27-A2A1-A20AF5BB84C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5FB6670-C8E9-4498-A6E3-39F46EA8872D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="8700" xr2:uid="{7C4DD652-79BF-4A73-ACB3-219C26059273}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,32 +47,32 @@
     <t>Title</t>
   </si>
   <si>
+    <t>Path</t>
+  </si>
+  <si>
     <t>present login</t>
   </si>
   <si>
+    <t>tests\TestCase1.xaml</t>
+  </si>
+  <si>
     <t>login</t>
   </si>
   <si>
+    <t>tests\TestCase2.xaml</t>
+  </si>
+  <si>
     <t>logout</t>
   </si>
   <si>
-    <t>C:\Users\akrao\OneDrive\Documents\UiPath\Assignment-13\tests\TestCase1.xaml</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>C:\Users\akrao\OneDrive\Documents\UiPath\Assignment-13\tests\TestCase2.xaml</t>
-  </si>
-  <si>
-    <t>C:\Users\akrao\OneDrive\Documents\UiPath\Assignment-13\tests\TestCase3.xaml</t>
+    <t>tests\TestCase3.xaml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,8 +101,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,9 +421,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0958FF14-535E-4F1E-B881-DD31570F9847}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,10 +437,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -440,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -454,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -468,9 +476,9 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
